--- a/demo/database/data/dataset_v6.xlsx
+++ b/demo/database/data/dataset_v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seantsang/Documents/work/ui_v4/demo/database/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seantsang/Documents/working/docpal-v6/demo/database/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EB9AE1-1FC9-4748-80F2-7BBA693522A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72081960-8624-B24A-861C-AC09A7C43A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="32420" windowHeight="19540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32500" yWindow="1200" windowWidth="30240" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1039">
   <si>
     <t>No.</t>
   </si>
@@ -3161,6 +3161,9 @@
   </si>
   <si>
     <t>Chief Financial Officer 2</t>
+  </si>
+  <si>
+    <t>Sales Representative 21</t>
   </si>
 </sst>
 </file>
@@ -3746,8 +3749,8 @@
       <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
+      <c r="D2" s="44" t="s">
+        <v>1038</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>8</v>
